--- a/report-009-manual-009.xlsx
+++ b/report-009-manual-009.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"baseline_commit": "1e97f84ce5ff67ae88a36c49c4fd718c16d1d8ca", "fix_commit": "6273160754495a331976bcfce6e1674b29cfc9fb", "fix_passed": true, "red_failed": true, "test_commit": "828a82a539e51907915f2b877eaa1fd5bfeb0d70"}</t>
+          <t>{"post_fix": {"commit": "6273160754495a331976bcfce6e1674b29cfc9fb", "result": "green", "trajectory_url": "未生成"}, "pre_fix": {"commit": "828a82a539e51907915f2b877eaa1fd5bfeb0d70", "result": "red", "trajectory_url": "未生成"}}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
